--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F1FB7B-9214-4AF5-9BE3-92DA246E0DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD1122B-B7D0-4011-9857-26E3891C5879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="простые" sheetId="5" r:id="rId3"/>
     <sheet name="составные" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные" sheetId="3" r:id="rId5"/>
+    <sheet name="ошибки" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
@@ -274,6 +275,15 @@
   </si>
   <si>
     <t>образовывать «воинскую часть» и делать с ней</t>
+  </si>
+  <si>
+    <t>пыльцын</t>
+  </si>
+  <si>
+    <t>Мне удалось установить</t>
+  </si>
+  <si>
+    <t>мне удалось установить</t>
   </si>
 </sst>
 </file>
@@ -601,13 +611,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -623,7 +633,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -631,7 +641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -639,7 +649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -647,7 +657,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -655,7 +665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -663,7 +673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -671,7 +681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -687,13 +697,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEAE8FF-D6D1-4BCA-92F8-1FC0A1E33D41}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="76.7109375" customWidth="1"/>
+    <col min="1" max="1" width="76.7265625" customWidth="1"/>
     <col min="2" max="2" width="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -701,7 +711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -709,7 +719,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -717,7 +727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -725,7 +735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -733,7 +743,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -741,7 +751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -749,7 +759,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -757,7 +767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -765,7 +775,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -773,7 +783,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -781,7 +791,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>48</v>
       </c>
@@ -789,7 +799,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -797,7 +807,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -805,7 +815,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>54</v>
       </c>
@@ -813,7 +823,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -821,7 +831,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>71</v>
       </c>
@@ -829,7 +839,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -837,7 +847,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -845,7 +855,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -853,7 +863,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -861,7 +871,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>69</v>
       </c>
@@ -869,7 +879,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -885,13 +895,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6931204F-D607-45BE-BF94-587C8B27C79D}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>65</v>
       </c>
@@ -907,13 +917,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED43094E-F29D-4F77-9E46-699CA581476C}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -921,7 +931,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -937,13 +947,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB7E2CD-11F1-40F5-94BE-FB52DF54CD99}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="71.28515625" customWidth="1"/>
-    <col min="2" max="2" width="71.7109375" customWidth="1"/>
+    <col min="1" max="1" width="71.26953125" customWidth="1"/>
+    <col min="2" max="2" width="71.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -951,7 +961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -959,7 +969,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -967,7 +977,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -975,7 +985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -983,12 +993,38 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>75</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{588E410B-1476-4B1E-843B-840A0C6B3AC8}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD1122B-B7D0-4011-9857-26E3891C5879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2B9563-1E80-45C4-9E52-596414C5745E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="составные" sheetId="4" r:id="rId4"/>
     <sheet name="неизменные" sheetId="3" r:id="rId5"/>
     <sheet name="ошибки" sheetId="6" r:id="rId6"/>
+    <sheet name="составные_длинные" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -610,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.6328125" customWidth="1"/>
     <col min="2" max="2" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -627,65 +628,57 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1030,4 +1023,26 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE8E230-72B6-4A17-BAA4-0D42C878A83F}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="37.81640625" customWidth="1"/>
+    <col min="2" max="2" width="50.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2B9563-1E80-45C4-9E52-596414C5745E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE981B5-2B43-490E-82F9-81CA12FA331B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE981B5-2B43-490E-82F9-81CA12FA331B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0F5145-8C82-40DD-AC6E-10738343D1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -611,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="53.6328125" customWidth="1"/>
@@ -620,69 +620,64 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B8">
+    <sortCondition ref="A1:A8"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1027,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE8E230-72B6-4A17-BAA4-0D42C878A83F}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.81640625" customWidth="1"/>
@@ -1042,6 +1037,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
